--- a/PBG/PBG_Mendoza_1970-2022_ordenado.xlsx
+++ b/PBG/PBG_Mendoza_1970-2022_ordenado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/971a82d91f2470ed/Escritorio/ECONOMIA/3 AÑO/Lab Ciencia de Datos/Proyecto historia economica/Proyecto-evolucion-salarios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Facultad\Proyecto-evolucion-salarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{A95B218E-9BA0-4EAA-B509-1EFB85E5B91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B35EC291-FDAE-4AFD-8BC9-1BA11580ED43}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0414E163-D956-41B0-926B-C138D1DA1D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas" sheetId="1" r:id="rId1"/>
@@ -426,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -485,12 +485,149 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF003366"/>
+          <bgColor rgb="FF1B2A4A"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -821,6 +958,497 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11059091512419023"/>
+          <c:y val="0.12754563714479189"/>
+          <c:w val="0.84835733216871545"/>
+          <c:h val="0.81730801809785458"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'PBI Ferreres (nacional)'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PBI (mill. $ de 1993)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'PBI Ferreres (nacional)'!$A$5:$A$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'PBI Ferreres (nacional)'!$B$5:$B$40</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>152643.77335610599</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>160860.95636173099</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>166912.606221553</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>170379.33445085399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>176760.97430606201</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>186316.01795022801</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>185210.551465686</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>185188.55213266</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>197015.02691173099</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>190666.38605606201</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>203891.651760017</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>207011.43217472499</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>195787.085571267</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>189602.24152446401</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>197400.610512652</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>201349.024597112</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>187351.74596487399</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>200726.11957615399</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>205926.37181563699</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>202022.16389395401</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>188010.819664468</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>184568.767080916</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>204093.82543139899</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>223701.26799433099</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>236504.98023157299</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>250307.88553631501</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>243186.10151946</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>256626.24305584701</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>277441.31762237998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>288122.80460772401</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>278369.01387171802</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>276172.18535265001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>263995.67436681699</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>235234.596752907</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>256022.46524751</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>279020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-78CC-4337-9430-E81571CD36C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="355619512"/>
+        <c:axId val="355618792"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="355619512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-419"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="355618792"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="355618792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-419"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="355619512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-419"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-419"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1780,6 +2408,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2335,7 +3003,564 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>104781</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8F7A54A-4B20-D871-4621-2B9291F8CCD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2377,15 +3602,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{741094FC-1EF8-4ACF-AD2A-75769E382932}" name="Tabla1" displayName="Tabla1" ref="A4:D57" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FEDC8F7D-677D-4C7F-90F9-A5C877AA19C5}" name="Tabla2" displayName="Tabla2" ref="A4:B40" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+  <autoFilter ref="A4:B40" xr:uid="{FEDC8F7D-677D-4C7F-90F9-A5C877AA19C5}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{85F6E0D9-6170-4F73-9A2B-FF281C4236B6}" name="Año" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{4E25473F-E3DE-47DE-A362-1897ACDB80CD}" name="PBI (mill. $ de 1993)" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{741094FC-1EF8-4ACF-AD2A-75769E382932}" name="Tabla1" displayName="Tabla1" ref="A4:D57" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A4:D57" xr:uid="{741094FC-1EF8-4ACF-AD2A-75769E382932}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A00E71CC-573E-4A5D-884A-71559B0D0878}" name="Año" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{365C3385-0229-438C-B36E-9788B3607800}" name="Tramo de origen" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{19FBF4BE-C44D-4711-A3AB-20102B1B4CCB}" name="PBG (miles $ ctes. de 1999)" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{A00E71CC-573E-4A5D-884A-71559B0D0878}" name="Año" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{365C3385-0229-438C-B36E-9788B3607800}" name="Tramo de origen" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{19FBF4BE-C44D-4711-A3AB-20102B1B4CCB}" name="PBG (miles $ ctes. de 1999)" dataDxfId="7">
       <calculatedColumnFormula>'PBG por tramo'!E11*'Coeficiente de empalme (B-C)'!$B$8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9892B746-E94B-4597-8310-A0CF79184942}" name="Variación anual (%)" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{9892B746-E94B-4597-8310-A0CF79184942}" name="Variación anual (%)" dataDxfId="6">
       <calculatedColumnFormula>C5/C4-1</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2573,19 +3809,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21"/>
     </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2593,7 +3829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2601,7 +3837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -2609,7 +3845,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -2617,7 +3853,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -2625,7 +3861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -2633,7 +3869,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -2641,7 +3877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -2649,7 +3885,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -2657,7 +3893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -2665,7 +3901,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -2685,7 +3921,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2694,7 +3930,7 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>20</v>
       </c>
@@ -2704,7 +3940,7 @@
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>62</v>
       </c>
@@ -2714,7 +3950,7 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
@@ -2734,7 +3970,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1970</v>
       </c>
@@ -2752,7 +3988,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>1971</v>
       </c>
@@ -2773,7 +4009,7 @@
         <v>6.6936796094821949E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>1972</v>
       </c>
@@ -2794,7 +4030,7 @@
         <v>6.5338955174785385E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1973</v>
       </c>
@@ -2815,7 +4051,7 @@
         <v>2.2651995733453001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>1974</v>
       </c>
@@ -2836,7 +4072,7 @@
         <v>0.11538989377761921</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>1975</v>
       </c>
@@ -2857,7 +4093,7 @@
         <v>-0.12591972832640208</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>1976</v>
       </c>
@@ -2878,7 +4114,7 @@
         <v>0.13752815315315314</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>1977</v>
       </c>
@@ -2899,7 +4135,7 @@
         <v>-5.7963123375819881E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>1978</v>
       </c>
@@ -2920,7 +4156,7 @@
         <v>0.11289178467277949</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>1979</v>
       </c>
@@ -2941,7 +4177,7 @@
         <v>0.13562322946175631</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>1980</v>
       </c>
@@ -2962,7 +4198,7 @@
         <v>-0.10770190208917996</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>1981</v>
       </c>
@@ -2983,7 +4219,7 @@
         <v>-0.18034199981362409</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>1982</v>
       </c>
@@ -3004,7 +4240,7 @@
         <v>2.4443623340818066E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>1983</v>
       </c>
@@ -3025,7 +4261,7 @@
         <v>0.16322170740504394</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1984</v>
       </c>
@@ -3046,7 +4282,7 @@
         <v>-3.5347994084816037E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>1985</v>
       </c>
@@ -3067,7 +4303,7 @@
         <v>-4.9030758579764577E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>1986</v>
       </c>
@@ -3085,7 +4321,7 @@
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>1987</v>
       </c>
@@ -3106,7 +4342,7 @@
         <v>1.2866920993226172E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>1988</v>
       </c>
@@ -3127,7 +4363,7 @@
         <v>-2.4272095391290271E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>1989</v>
       </c>
@@ -3148,7 +4384,7 @@
         <v>-4.1830356974057792E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>1990</v>
       </c>
@@ -3169,7 +4405,7 @@
         <v>8.5631979795586233E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>1991</v>
       </c>
@@ -3190,7 +4426,7 @@
         <v>2.3467533030789411E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>1992</v>
       </c>
@@ -3211,7 +4447,7 @@
         <v>6.891928854029028E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>1993</v>
       </c>
@@ -3232,7 +4468,7 @@
         <v>7.0263705134627763E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>1991</v>
       </c>
@@ -3250,7 +4486,7 @@
       </c>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>1992</v>
       </c>
@@ -3271,7 +4507,7 @@
         <v>8.4730252294494379E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>1993</v>
       </c>
@@ -3292,7 +4528,7 @@
         <v>0.10326652390160662</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>1994</v>
       </c>
@@ -3313,7 +4549,7 @@
         <v>4.3357563520997067E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>1995</v>
       </c>
@@ -3334,7 +4570,7 @@
         <v>-2.3365801855606549E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>1996</v>
       </c>
@@ -3355,7 +4591,7 @@
         <v>2.8645327411909172E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>1997</v>
       </c>
@@ -3376,7 +4612,7 @@
         <v>9.4721977867370466E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>1998</v>
       </c>
@@ -3397,7 +4633,7 @@
         <v>6.5387282637103139E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>1999</v>
       </c>
@@ -3418,7 +4654,7 @@
         <v>-2.483910331204775E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>2000</v>
       </c>
@@ -3439,7 +4675,7 @@
         <v>-2.7081718351090522E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>2001</v>
       </c>
@@ -3460,7 +4696,7 @@
         <v>-7.5432354387124145E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>2002</v>
       </c>
@@ -3481,7 +4717,7 @@
         <v>-6.6177566696846712E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>2003</v>
       </c>
@@ -3502,7 +4738,7 @@
         <v>0.20171019152567271</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>2004</v>
       </c>
@@ -3520,7 +4756,7 @@
       </c>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>2005</v>
       </c>
@@ -3541,7 +4777,7 @@
         <v>4.6513803403071208E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>2006</v>
       </c>
@@ -3562,7 +4798,7 @@
         <v>7.7195222681360143E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>2007</v>
       </c>
@@ -3583,7 +4819,7 @@
         <v>4.1716449950309986E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>2008</v>
       </c>
@@ -3604,7 +4840,7 @@
         <v>2.3057070180426908E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>2009</v>
       </c>
@@ -3625,7 +4861,7 @@
         <v>-2.7891879130777508E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>2010</v>
       </c>
@@ -3646,7 +4882,7 @@
         <v>4.4223332102990343E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>2011</v>
       </c>
@@ -3667,7 +4903,7 @@
         <v>3.5977714375441838E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>2012</v>
       </c>
@@ -3688,7 +4924,7 @@
         <v>-1.4156037666630872E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>2013</v>
       </c>
@@ -3709,7 +4945,7 @@
         <v>4.9200721123227487E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>2014</v>
       </c>
@@ -3730,7 +4966,7 @@
         <v>-3.6842630268091314E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>2015</v>
       </c>
@@ -3751,7 +4987,7 @@
         <v>3.6643876408434695E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>2016</v>
       </c>
@@ -3772,7 +5008,7 @@
         <v>-5.754253235777973E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>2017</v>
       </c>
@@ -3793,7 +5029,7 @@
         <v>2.1123875796110525E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>2018</v>
       </c>
@@ -3814,7 +5050,7 @@
         <v>-5.1177207495317623E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>2019</v>
       </c>
@@ -3835,7 +5071,7 @@
         <v>-1.2863316386648838E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>2020</v>
       </c>
@@ -3856,7 +5092,7 @@
         <v>-7.9652330003202265E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>2021</v>
       </c>
@@ -3877,7 +5113,7 @@
         <v>0.10477832536319798</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>2022</v>
       </c>
@@ -3911,19 +5147,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="21"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>21</v>
       </c>
@@ -3931,7 +5167,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1970</v>
       </c>
@@ -3939,7 +5175,7 @@
         <v>4.7536083333333301E-10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1971</v>
       </c>
@@ -3947,7 +5183,7 @@
         <v>6.4042000000000005E-10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>1972</v>
       </c>
@@ -3955,7 +5191,7 @@
         <v>1.0147766666666699E-9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>1973</v>
       </c>
@@ -3963,7 +5199,7 @@
         <v>1.62672083333333E-9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1974</v>
       </c>
@@ -3971,7 +5207,7 @@
         <v>2.02065416666667E-9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>1975</v>
       </c>
@@ -3979,7 +5215,7 @@
         <v>5.71426666666667E-9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>1976</v>
       </c>
@@ -3987,7 +5223,7 @@
         <v>3.1086300000000001E-8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>1977</v>
       </c>
@@ -3995,7 +5231,7 @@
         <v>8.5808050000000006E-8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>1978</v>
       </c>
@@ -4003,7 +5239,7 @@
         <v>2.3640875E-7</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>1979</v>
       </c>
@@ -4011,7 +5247,7 @@
         <v>6.1350683333333398E-7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>1980</v>
       </c>
@@ -4019,7 +5255,7 @@
         <v>1.2317020000000001E-6</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>1981</v>
       </c>
@@ -4027,7 +5263,7 @@
         <v>2.5185499999999998E-6</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>1982</v>
       </c>
@@ -4035,7 +5271,7 @@
         <v>6.6685833333333299E-6</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>1983</v>
       </c>
@@ -4043,7 +5279,7 @@
         <v>2.95951416666667E-5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>1984</v>
       </c>
@@ -4051,7 +5287,7 @@
         <v>2.1507783333333299E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1985</v>
       </c>
@@ -4059,7 +5295,7 @@
         <v>1.6607925000000001E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>1986</v>
       </c>
@@ -4067,7 +5303,7 @@
         <v>3.1570041666666702E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>1987</v>
       </c>
@@ -4075,7 +5311,7 @@
         <v>7.30324166666667E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>1988</v>
       </c>
@@ -4083,7 +5319,7 @@
         <v>3.2349999999999997E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>1989</v>
       </c>
@@ -4091,7 +5327,7 @@
         <v>1.0285535833333299</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>1990</v>
       </c>
@@ -4099,7 +5335,7 @@
         <v>24.828900000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>1991</v>
       </c>
@@ -4107,7 +5343,7 @@
         <v>67.453100000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>1992</v>
       </c>
@@ -4115,7 +5351,7 @@
         <v>84.248900000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>1993</v>
       </c>
@@ -4123,7 +5359,7 @@
         <v>93.188999999999993</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>1994</v>
       </c>
@@ -4131,7 +5367,7 @@
         <v>97.081800000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>1995</v>
       </c>
@@ -4139,7 +5375,7 @@
         <v>100.35939999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>1996</v>
       </c>
@@ -4147,7 +5383,7 @@
         <v>100.51560000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>1997</v>
       </c>
@@ -4155,7 +5391,7 @@
         <v>101.04689999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>1998</v>
       </c>
@@ -4163,7 +5399,7 @@
         <v>101.9813</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>1999</v>
       </c>
@@ -4171,7 +5407,7 @@
         <v>100.7915</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>2000</v>
       </c>
@@ -4179,7 +5415,7 @@
         <v>99.844899999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>2001</v>
       </c>
@@ -4187,7 +5423,7 @@
         <v>98.781666666666695</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>2002</v>
       </c>
@@ -4195,7 +5431,7 @@
         <v>124.33499999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>2003</v>
       </c>
@@ -4203,7 +5439,7 @@
         <v>141.05000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>2004</v>
       </c>
@@ -4211,7 +5447,7 @@
         <v>147.28</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>2005</v>
       </c>
@@ -4219,7 +5455,7 @@
         <v>167.48</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>2006</v>
       </c>
@@ -4227,7 +5463,7 @@
         <v>179.08</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>2007</v>
       </c>
@@ -4235,7 +5471,7 @@
         <v>194.89</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>2008</v>
       </c>
@@ -4243,7 +5479,7 @@
         <v>238.54535999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>2009</v>
       </c>
@@ -4251,7 +5487,7 @@
         <v>287.92424951999999</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>2010</v>
       </c>
@@ -4259,7 +5495,7 @@
         <v>334.56797794224002</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>2011</v>
       </c>
@@ -4267,7 +5503,7 @@
         <v>427.91244378812502</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>2012</v>
       </c>
@@ -4275,7 +5511,7 @@
         <v>527.61604319075798</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>2013</v>
       </c>
@@ -4283,7 +5519,7 @@
         <v>650.55058125420499</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>2014</v>
       </c>
@@ -4291,7 +5527,7 @@
         <v>844.41465446795803</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>2015</v>
       </c>
@@ -4299,7 +5535,7 @@
         <v>1192.3134921087601</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>2016</v>
       </c>
@@ -4307,7 +5543,7 @@
         <v>1513.04582148601</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>2017</v>
       </c>
@@ -4315,7 +5551,7 @@
         <v>2066.8205921498902</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>2018</v>
       </c>
@@ -4323,7 +5559,7 @@
         <v>2546.32296952867</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>2019</v>
       </c>
@@ -4331,7 +5567,7 @@
         <v>3860.2256218054599</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>2020</v>
       </c>
@@ -4339,7 +5575,7 @@
         <v>5921.5861038495796</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>2021</v>
       </c>
@@ -4359,14 +5595,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>36</v>
       </c>
@@ -4374,7 +5610,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>37</v>
       </c>
@@ -4382,7 +5618,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
@@ -4391,12 +5627,12 @@
         <v>26.136104337887964</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -4405,12 +5641,12 @@
         <v>1.0815815171318504</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
         <v>42</v>
       </c>
@@ -4418,19 +5654,19 @@
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -4450,317 +5686,317 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="21"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="24"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="22"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
         <v>1969</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="24">
         <v>152643.77335610599</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
         <v>1970</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="24">
         <v>160860.95636173099</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
         <v>1971</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="24">
         <v>166912.606221553</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
         <v>1972</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="24">
         <v>170379.33445085399</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
         <v>1973</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="24">
         <v>176760.97430606201</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
         <v>1974</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="24">
         <v>186316.01795022801</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
         <v>1975</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="24">
         <v>185210.551465686</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
         <v>1976</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="24">
         <v>185188.55213266</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
         <v>1977</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="24">
         <v>197015.02691173099</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
         <v>1978</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="24">
         <v>190666.38605606201</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
         <v>1979</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="24">
         <v>203891.651760017</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
         <v>1980</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="24">
         <v>207011.43217472499</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
         <v>1981</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="24">
         <v>195787.085571267</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
         <v>1982</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="24">
         <v>189602.24152446401</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
         <v>1983</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="24">
         <v>197400.610512652</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
         <v>1984</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="24">
         <v>201349.024597112</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
         <v>1985</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="24">
         <v>187351.74596487399</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
         <v>1986</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="24">
         <v>200726.11957615399</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
         <v>1987</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="24">
         <v>205926.37181563699</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
         <v>1988</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="24">
         <v>202022.16389395401</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="11">
         <v>1989</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="24">
         <v>188010.819664468</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
         <v>1990</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="24">
         <v>184568.767080916</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
         <v>1991</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="24">
         <v>204093.82543139899</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
         <v>1992</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="24">
         <v>223701.26799433099</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
         <v>1993</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="24">
         <v>236504.98023157299</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
         <v>1994</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="24">
         <v>250307.88553631501</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
         <v>1995</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="24">
         <v>243186.10151946</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
         <v>1996</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="24">
         <v>256626.24305584701</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
         <v>1997</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="24">
         <v>277441.31762237998</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
         <v>1998</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="24">
         <v>288122.80460772401</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
         <v>1999</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="24">
         <v>278369.01387171802</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
         <v>2000</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="24">
         <v>276172.18535265001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
         <v>2001</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="24">
         <v>263995.67436681699</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
         <v>2002</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="24">
         <v>235234.596752907</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
         <v>2003</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="24">
         <v>256022.46524751</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="17">
         <v>2004</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="25">
         <v>279020</v>
       </c>
     </row>
@@ -4771,19 +6007,23 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>45</v>
       </c>
@@ -4791,7 +6031,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>60</v>
       </c>
@@ -4799,7 +6039,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>46</v>
       </c>
@@ -4808,7 +6048,7 @@
         <v>7.1386437005970027E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
@@ -4817,12 +6057,12 @@
         <v>649.43174288959028</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
         <v>48</v>
       </c>
@@ -4830,13 +6070,13 @@
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -4856,15 +6096,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="27.44140625" customWidth="1"/>
-    <col min="4" max="4" width="31.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>49</v>
       </c>
@@ -4872,7 +6112,7 @@
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>59</v>
       </c>
@@ -4880,7 +6120,7 @@
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
@@ -4894,7 +6134,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1970</v>
       </c>
@@ -4907,7 +6147,7 @@
       </c>
       <c r="D5" s="12"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1971</v>
       </c>
@@ -4923,7 +6163,7 @@
         <v>6.6936796094821949E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1972</v>
       </c>
@@ -4939,7 +6179,7 @@
         <v>6.5338955174785163E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1973</v>
       </c>
@@ -4955,7 +6195,7 @@
         <v>2.2651995733453223E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>1974</v>
       </c>
@@ -4971,7 +6211,7 @@
         <v>0.11538989377761943</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>1975</v>
       </c>
@@ -4987,7 +6227,7 @@
         <v>-0.12591972832640219</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>1976</v>
       </c>
@@ -5003,7 +6243,7 @@
         <v>0.13752815315315314</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>1977</v>
       </c>
@@ -5019,7 +6259,7 @@
         <v>-5.7963123375819881E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>1978</v>
       </c>
@@ -5035,7 +6275,7 @@
         <v>0.11289178467277927</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>1979</v>
       </c>
@@ -5051,7 +6291,7 @@
         <v>0.13562322946175653</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>1980</v>
       </c>
@@ -5067,7 +6307,7 @@
         <v>-0.10770190208917985</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>1981</v>
       </c>
@@ -5083,7 +6323,7 @@
         <v>-0.18034199981362431</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>1982</v>
       </c>
@@ -5099,7 +6339,7 @@
         <v>2.4443623340818288E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>1983</v>
       </c>
@@ -5115,7 +6355,7 @@
         <v>0.16322170740504371</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>1984</v>
       </c>
@@ -5131,7 +6371,7 @@
         <v>-3.5347994084815926E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>1985</v>
       </c>
@@ -5147,7 +6387,7 @@
         <v>-4.9030758579764688E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>1986</v>
       </c>
@@ -5163,7 +6403,7 @@
         <v>7.1386437005970027E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1987</v>
       </c>
@@ -5179,7 +6419,7 @@
         <v>1.2866920993226394E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>1988</v>
       </c>
@@ -5195,7 +6435,7 @@
         <v>-2.4272095391290383E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>1989</v>
       </c>
@@ -5211,7 +6451,7 @@
         <v>-4.1830356974057792E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>1990</v>
       </c>
@@ -5227,7 +6467,7 @@
         <v>8.5631979795586233E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>1991</v>
       </c>
@@ -5243,7 +6483,7 @@
         <v>-2.1619949021637663E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>1992</v>
       </c>
@@ -5259,7 +6499,7 @@
         <v>8.4730252294494379E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>1993</v>
       </c>
@@ -5275,7 +6515,7 @@
         <v>0.10326652390160662</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>1994</v>
       </c>
@@ -5291,7 +6531,7 @@
         <v>4.3357563520997067E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>1995</v>
       </c>
@@ -5307,7 +6547,7 @@
         <v>-2.336580185560666E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>1996</v>
       </c>
@@ -5323,7 +6563,7 @@
         <v>2.8645327411909172E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>1997</v>
       </c>
@@ -5339,7 +6579,7 @@
         <v>9.4721977867370466E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>1998</v>
       </c>
@@ -5355,7 +6595,7 @@
         <v>6.5387282637103139E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>1999</v>
       </c>
@@ -5371,7 +6611,7 @@
         <v>-2.4839103312047861E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>2000</v>
       </c>
@@ -5387,7 +6627,7 @@
         <v>-2.7081718351090411E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>2001</v>
       </c>
@@ -5403,7 +6643,7 @@
         <v>-7.5432354387124145E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>2002</v>
       </c>
@@ -5419,7 +6659,7 @@
         <v>-6.6177566696846712E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>2003</v>
       </c>
@@ -5435,7 +6675,7 @@
         <v>0.20171019152567249</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>2004</v>
       </c>
@@ -5451,7 +6691,7 @@
         <v>0.16434808068002815</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>2005</v>
       </c>
@@ -5467,7 +6707,7 @@
         <v>4.6513803403071208E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>2006</v>
       </c>
@@ -5483,7 +6723,7 @@
         <v>7.7195222681360143E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>2007</v>
       </c>
@@ -5499,7 +6739,7 @@
         <v>4.1716449950309986E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>2008</v>
       </c>
@@ -5515,7 +6755,7 @@
         <v>2.3057070180426908E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>2009</v>
       </c>
@@ -5531,7 +6771,7 @@
         <v>-2.7891879130777397E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>2010</v>
       </c>
@@ -5547,7 +6787,7 @@
         <v>4.4223332102990343E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
         <v>2011</v>
       </c>
@@ -5563,7 +6803,7 @@
         <v>3.5977714375441838E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>2012</v>
       </c>
@@ -5579,7 +6819,7 @@
         <v>-1.4156037666630872E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>2013</v>
       </c>
@@ -5595,7 +6835,7 @@
         <v>4.9200721123227709E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>2014</v>
       </c>
@@ -5611,7 +6851,7 @@
         <v>-3.6842630268091425E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>2015</v>
       </c>
@@ -5627,7 +6867,7 @@
         <v>3.6643876408434695E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>2016</v>
       </c>
@@ -5643,7 +6883,7 @@
         <v>-5.754253235777973E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>2017</v>
       </c>
@@ -5659,7 +6899,7 @@
         <v>2.1123875796110525E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>2018</v>
       </c>
@@ -5675,7 +6915,7 @@
         <v>-5.1177207495317623E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>2019</v>
       </c>
@@ -5691,7 +6931,7 @@
         <v>-1.2863316386648838E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>2020</v>
       </c>
@@ -5707,7 +6947,7 @@
         <v>-7.9652330003202265E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>2021</v>
       </c>
@@ -5723,7 +6963,7 @@
         <v>0.1047783253631982</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="17">
         <v>2022</v>
       </c>
